--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -34203,12 +34203,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34233,12 +34233,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N195" t="n">
@@ -34255,87 +34255,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34362,7 +34343,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -34411,98 +34392,23 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -34601,17 +34507,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34650,76 +34556,170 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34751,12 +34751,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34803,87 +34803,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34910,7 +34891,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -34959,98 +34940,23 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -35121,6 +35027,245 @@
         </is>
       </c>
       <c r="BC199" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -35242,7 +35387,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -35252,7 +35397,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1258</v>
+        <v>1422</v>
       </c>
       <c r="O152" t="n">
-        <v>1258</v>
+        <v>1422</v>
       </c>
       <c r="R152" t="n">
-        <v>0.5890542671230413</v>
+        <v>0.665846715301244</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -30990,13 +30990,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>244</v>
+        <v>416</v>
       </c>
       <c r="O177" t="n">
-        <v>244</v>
+        <v>416</v>
       </c>
       <c r="R177" t="n">
-        <v>0.1142521789968379</v>
+        <v>0.194790600256904</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -31096,12 +31096,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -31135,100 +31135,84 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O178" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>0.0004246542694163248</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -31255,7 +31239,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -31304,98 +31288,23 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -31494,17 +31403,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31538,81 +31447,175 @@
         </is>
       </c>
       <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
         <v>1</v>
       </c>
-      <c r="O180" t="n">
-        <v>1</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31644,12 +31647,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -31683,100 +31686,81 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31803,7 +31787,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -31852,98 +31836,23 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN182" t="b">
-        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -32042,17 +31951,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -32077,7 +31986,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -32091,76 +32000,170 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32192,12 +32195,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32236,9 +32239,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="P184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -32247,77 +32247,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32344,7 +32335,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -32396,98 +32387,18 @@
       <c r="P185" t="n">
         <v>0</v>
       </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -32581,17 +32492,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -32616,7 +32527,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -32630,76 +32541,168 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32731,12 +32734,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -32775,9 +32778,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -32786,77 +32786,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32883,7 +32874,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -32935,98 +32926,18 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -33120,17 +33031,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33155,7 +33066,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -33169,76 +33080,168 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33270,12 +33273,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33314,9 +33317,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -33325,77 +33325,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33422,7 +33413,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -33474,98 +33465,18 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -33659,17 +33570,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -33694,7 +33605,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -33708,76 +33619,168 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33809,12 +33812,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -33848,93 +33851,81 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>1</v>
-      </c>
-      <c r="P193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33961,7 +33952,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -34013,98 +34004,18 @@
       <c r="P194" t="n">
         <v>1</v>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R194" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -34198,17 +34109,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34233,7 +34144,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34242,81 +34153,173 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P195" t="n">
+        <v>1</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34348,12 +34351,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34378,12 +34381,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N196" t="n">
@@ -34400,87 +34403,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34507,17 +34491,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34542,12 +34526,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -34556,98 +34540,21 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -34656,22 +34563,17 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1195</t>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -34679,47 +34581,47 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34746,17 +34648,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34781,12 +34683,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -34795,76 +34697,168 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34896,12 +34890,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -34950,7 +34944,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -34970,7 +34964,7 @@
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
@@ -34980,7 +34974,7 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -34988,47 +34982,47 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35060,12 +35054,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35106,22 +35100,22 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>Zikafeber-infeksjon</t>
+          <t>Zika virus</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -35146,7 +35140,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -35181,17 +35175,17 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -35209,7 +35203,7 @@
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
@@ -35219,7 +35213,7 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -35227,45 +35221,593 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV200" t="inlineStr">
+      <c r="AV202" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW200" t="inlineStr">
+      <c r="AW202" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX200" t="inlineStr">
+      <c r="AX202" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY200" t="inlineStr">
+      <c r="AY202" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ200" t="inlineStr">
+      <c r="AZ202" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA200" t="inlineStr">
+      <c r="BA202" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB200" t="inlineStr">
+      <c r="BB202" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC200" t="inlineStr">
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -35387,7 +35929,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -35397,7 +35939,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -35417,7 +35959,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -35449,7 +35991,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8625</v>
+        <v>8967</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -35813,6 +35813,151 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="n">
+        <v>2</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
+      <c r="AT204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35846,7 +35991,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -35929,7 +36074,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -35939,7 +36084,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -35991,7 +36136,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8967</v>
+        <v>8969</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1422</v>
+        <v>1490</v>
       </c>
       <c r="O152" t="n">
-        <v>1422</v>
+        <v>1490</v>
       </c>
       <c r="R152" t="n">
-        <v>0.665846715301244</v>
+        <v>0.697687486497084</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -30990,13 +30990,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>416</v>
+        <v>723</v>
       </c>
       <c r="O177" t="n">
-        <v>416</v>
+        <v>723</v>
       </c>
       <c r="R177" t="n">
-        <v>0.194790600256904</v>
+        <v>0.3385423172734173</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -34890,12 +34890,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -34929,100 +34929,81 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>0.007491946163727075</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35030,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -35098,98 +35079,23 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -35288,17 +35194,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35337,76 +35243,170 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35438,12 +35438,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35490,87 +35490,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35597,7 +35578,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -35646,98 +35627,23 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -35836,123 +35742,362 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>D051</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>Zika virus disease</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
         <is>
           <t>寨卡病毒病</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N204" t="n">
+      <c r="N205" t="n">
         <v>2</v>
       </c>
-      <c r="O204" t="n">
+      <c r="O205" t="n">
         <v>2</v>
       </c>
-      <c r="R204" t="n">
+      <c r="R205" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S204" t="inlineStr">
+      <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO204" t="inlineStr">
+      <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP204" t="inlineStr">
+      <c r="AP205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR204" t="inlineStr">
+      <c r="AR205" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS204" t="inlineStr"/>
-      <c r="AT204" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU204" t="inlineStr">
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV204" t="inlineStr">
+      <c r="AV205" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW204" t="inlineStr">
+      <c r="AW205" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX204" t="inlineStr">
+      <c r="AX205" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY204" t="inlineStr">
+      <c r="AY205" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ204" t="inlineStr">
+      <c r="AZ205" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA204" t="inlineStr">
+      <c r="BA205" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB204" t="inlineStr">
+      <c r="BB205" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC204" t="inlineStr">
+      <c r="BC205" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -36074,7 +36219,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -36084,7 +36229,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -36136,7 +36281,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8969</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -36103,6 +36103,400 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36219,7 +36613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -36229,7 +36623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -36249,7 +36643,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1490</v>
+        <v>1539</v>
       </c>
       <c r="O152" t="n">
-        <v>1490</v>
+        <v>1539</v>
       </c>
       <c r="R152" t="n">
-        <v>0.697687486497084</v>
+        <v>0.7206315716234982</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -30990,13 +30990,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>723</v>
+        <v>870</v>
       </c>
       <c r="O177" t="n">
-        <v>723</v>
+        <v>870</v>
       </c>
       <c r="R177" t="n">
-        <v>0.3385423172734173</v>
+        <v>0.4073745726526597</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -31647,12 +31647,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -31686,13 +31686,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -31725,42 +31725,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -31792,12 +31792,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -31831,100 +31831,81 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31951,7 +31932,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -32000,98 +31981,23 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -32190,17 +32096,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32225,7 +32131,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -32239,76 +32145,170 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32340,12 +32340,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32384,9 +32384,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -32395,77 +32392,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32492,7 +32480,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -32544,98 +32532,18 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -32729,17 +32637,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -32764,7 +32672,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -32778,76 +32686,168 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="R187" t="n">
-        <v>0</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32879,12 +32879,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -32923,9 +32923,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -32934,77 +32931,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33031,7 +33019,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -33083,98 +33071,18 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -33268,17 +33176,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33303,7 +33211,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -33317,76 +33225,168 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33418,12 +33418,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33462,9 +33462,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="P191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -33473,77 +33470,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33570,7 +33558,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -33622,98 +33610,18 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -33807,17 +33715,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -33842,7 +33750,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -33856,76 +33764,168 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33957,12 +33957,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -33996,93 +33996,81 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>1</v>
-      </c>
-      <c r="P194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34109,7 +34097,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -34161,98 +34149,18 @@
       <c r="P195" t="n">
         <v>1</v>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R195" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -34346,17 +34254,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34381,7 +34289,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -34390,81 +34298,173 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P196" t="n">
+        <v>1</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34496,12 +34496,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34540,9 +34540,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="P197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -34551,77 +34548,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34648,7 +34636,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -34700,98 +34688,18 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -34885,17 +34793,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -34920,90 +34828,182 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>16</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.007491946163727075</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35035,12 +35035,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35074,100 +35074,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>0.02762655147874359</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -35194,7 +35175,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -35243,98 +35224,23 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1195</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -35433,17 +35339,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35482,76 +35388,170 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35583,12 +35583,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35635,87 +35635,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35742,7 +35723,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -35791,98 +35772,23 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>SER_NO_FHI_513_MONTHLY</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_513_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Zikafeber-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -35981,17 +35887,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36016,7 +35922,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36025,81 +35931,175 @@
         </is>
       </c>
       <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT205" t="n">
         <v>2</v>
       </c>
-      <c r="O205" t="n">
-        <v>2</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO205" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP205" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
-      <c r="AT205" t="n">
-        <v>0</v>
-      </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36131,12 +36131,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36170,93 +36170,81 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36283,7 +36271,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -36335,98 +36323,18 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ZIKA</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Zika</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -36492,6 +36400,782 @@
         </is>
       </c>
       <c r="BC207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -36530,7 +37214,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -36613,7 +37297,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -36623,7 +37307,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -36643,7 +37327,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -36675,7 +37359,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9360</v>
+        <v>9599</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -32160,13 +32160,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="O183" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="R183" t="n">
-        <v>0.4073745726526597</v>
+        <v>0.4635641688806129</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -37024,13 +37024,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="O210" t="n">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="R210" t="n">
-        <v>0.02762655147874359</v>
+        <v>0.08568913424762843</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -39128,6 +39128,1093 @@
       <c r="BC221" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
+      <c r="AT222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" t="n">
+        <v>1</v>
+      </c>
+      <c r="P223" t="n">
+        <v>1</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="n">
+        <v>1</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
+      <c r="AT227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39164,7 +40251,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -39247,7 +40334,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -39257,7 +40344,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -39277,7 +40364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -39309,7 +40396,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9600</v>
+        <v>9845</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -29132,7 +29132,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4448,6 +4583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4996,6 +5136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5141,6 +5286,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5529,7 +5679,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -5692,6 +5842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6382,6 +6537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7072,6 +7232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7762,6 +7927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8452,6 +8622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8597,6 +8772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8733,6 +8913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8869,6 +9054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9005,6 +9195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9141,6 +9336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9277,6 +9477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9413,6 +9618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9549,6 +9759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9685,6 +9900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9821,6 +10041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9957,6 +10182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10093,6 +10323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10229,6 +10464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10365,6 +10605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10501,6 +10746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10637,6 +10887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10773,6 +11028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10909,6 +11169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11045,6 +11310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11181,6 +11451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11317,6 +11592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11453,6 +11733,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11589,6 +11874,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11725,6 +12015,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11861,6 +12156,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11997,6 +12297,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12133,6 +12438,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12272,6 +12582,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12820,6 +13135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12965,6 +13285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13353,7 +13678,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -14058,6 +14383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14748,6 +15078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15438,6 +15773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16128,6 +16468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16276,6 +16621,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16421,6 +16771,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16557,6 +16912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16693,6 +17053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16829,6 +17194,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16965,6 +17335,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17101,6 +17476,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17237,6 +17617,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17373,6 +17758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17509,6 +17899,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17645,6 +18040,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17781,6 +18181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17917,6 +18322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18053,6 +18463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18189,6 +18604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18325,6 +18745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18461,6 +18886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18597,6 +19027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18733,6 +19168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18869,6 +19309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19005,6 +19450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19141,6 +19591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19277,6 +19732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19413,6 +19873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19549,6 +20014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19685,6 +20155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19821,6 +20296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19957,6 +20437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20096,6 +20581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20644,6 +21134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20789,6 +21284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21177,7 +21677,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -21882,6 +22382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22572,6 +23077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23262,6 +23772,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23952,6 +24467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24491,6 +25011,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24636,6 +25161,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24772,6 +25302,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24908,6 +25443,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25044,6 +25584,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25180,6 +25725,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25316,6 +25866,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25452,6 +26007,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25588,6 +26148,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25724,6 +26289,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25860,6 +26430,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25996,6 +26571,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26132,6 +26712,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26268,6 +26853,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26404,6 +26994,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26540,6 +27135,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27276,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26812,6 +27417,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26948,6 +27558,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27084,6 +27699,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27220,6 +27840,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27356,6 +27981,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27492,6 +28122,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27628,6 +28263,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27764,6 +28404,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27900,6 +28545,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28036,6 +28686,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28172,6 +28827,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28311,6 +28971,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28859,6 +29524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29004,6 +29674,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29392,7 +30067,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -29703,6 +30378,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30393,6 +31073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31083,6 +31768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31773,6 +32463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32312,6 +33007,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32457,6 +33157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32593,6 +33298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32729,6 +33439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32865,6 +33580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33001,6 +33721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33137,6 +33862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33273,6 +34003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33409,6 +34144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33545,6 +34285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33681,6 +34426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33817,6 +34567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33953,6 +34708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34089,6 +34849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34225,6 +34990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34361,6 +35131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34497,6 +35272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34633,6 +35413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34769,6 +35554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34905,6 +35695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35041,6 +35836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35177,6 +35977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35313,6 +36118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35449,6 +36259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35585,6 +36400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35721,6 +36541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35857,6 +36682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35993,6 +36823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36132,6 +36967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36680,6 +37520,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36825,6 +37670,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37213,7 +38063,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -37524,6 +38374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38214,6 +39069,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38904,6 +39764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39594,6 +40459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40284,6 +41154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40823,6 +41698,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40968,6 +41848,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41104,6 +41989,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41240,6 +42130,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41376,6 +42271,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41512,6 +42412,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41648,6 +42553,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41784,6 +42694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41920,6 +42835,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42056,6 +42976,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42192,6 +43117,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42328,6 +43258,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42464,6 +43399,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42600,6 +43540,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42736,6 +43681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42872,6 +43822,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43008,6 +43963,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43144,6 +44104,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43280,6 +44245,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43416,6 +44386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43552,6 +44527,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43688,6 +44668,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43824,6 +44809,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43960,6 +44950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44096,6 +45091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44232,6 +45232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44368,6 +45373,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44504,6 +45514,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44643,6 +45658,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45581,6 +46601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45726,6 +46751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46114,7 +47144,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -46564,6 +47594,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47248,6 +48283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47932,6 +48972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48616,6 +49661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49155,6 +50205,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49300,6 +50355,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49436,6 +50496,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49572,6 +50637,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49708,6 +50778,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49844,6 +50919,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49980,6 +51060,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50116,6 +51201,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50252,6 +51342,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50388,6 +51483,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50524,6 +51624,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50660,6 +51765,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50796,6 +51906,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50932,6 +52047,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51068,6 +52188,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51204,6 +52329,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51340,6 +52470,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51476,6 +52611,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51612,6 +52752,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51748,6 +52893,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51884,6 +53034,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52020,6 +53175,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52156,6 +53316,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52292,6 +53457,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52428,6 +53598,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52564,6 +53739,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52700,6 +53880,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52836,6 +54021,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52975,6 +54165,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54303,6 +55498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54448,6 +55648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54836,7 +56041,7 @@
       </c>
       <c r="AM354" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN354" t="b">
@@ -55141,6 +56346,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55825,6 +57035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56509,6 +57724,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57193,6 +58413,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57877,6 +59102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58022,6 +59252,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58158,6 +59393,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58294,6 +59534,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58430,6 +59675,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58566,6 +59816,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58702,6 +59957,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58838,6 +60098,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58974,6 +60239,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59110,6 +60380,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59246,6 +60521,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59382,6 +60662,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59518,6 +60803,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59654,6 +60944,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59790,6 +61085,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59926,6 +61226,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60062,6 +61367,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60198,6 +61508,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60334,6 +61649,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60470,6 +61790,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60606,6 +61931,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60742,6 +62072,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60878,6 +62213,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61014,6 +62354,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61150,6 +62495,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61286,6 +62636,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61422,6 +62777,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61558,6 +62918,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61697,6 +63062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63025,6 +64395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63170,6 +64545,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63558,7 +64938,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -66413,6 +67793,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66558,6 +67943,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66694,6 +68084,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66830,6 +68225,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66966,6 +68366,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67102,6 +68507,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67238,6 +68648,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67374,6 +68789,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67510,6 +68930,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67646,6 +69071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67782,6 +69212,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67918,6 +69353,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68054,6 +69494,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68190,6 +69635,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68326,6 +69776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68462,6 +69917,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68598,6 +70058,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68734,6 +70199,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68870,6 +70340,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69006,6 +70481,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69142,6 +70622,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69278,6 +70763,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69414,6 +70904,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69550,6 +71045,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69686,6 +71186,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69822,6 +71327,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO451" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69958,6 +71468,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO452" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70094,6 +71609,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70633,6 +72153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO456" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71021,7 +72546,7 @@
       </c>
       <c r="AM458" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN458" t="b">
@@ -72891,12 +74416,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -72921,90 +74446,102 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N469" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O469" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0</v>
       </c>
       <c r="R469" t="n">
-        <v>0.0004668273620270607</v>
+        <v>0</v>
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>ibge_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO469" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP469" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR469" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS469" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ469" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS469" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
+        </is>
+      </c>
       <c r="AT469" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU469" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV469" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW469" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX469" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY469" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ469" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA469" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB469" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC469" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73031,17 +74568,17 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -73066,12 +74603,12 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N470" t="n">
@@ -73080,23 +74617,101 @@
       <c r="O470" t="n">
         <v>0</v>
       </c>
-      <c r="R470" t="n">
-        <v>0</v>
-      </c>
-      <c r="S470" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P470" t="n">
+        <v>0</v>
       </c>
       <c r="U470" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1195</t>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ZIKA</t>
+        </is>
+      </c>
+      <c r="W470" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>Zika</t>
+        </is>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z470" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA470" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB470" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC470" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD470" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE470" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF470" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG470" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH470" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI470" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ470" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK470" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM470" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN470" t="b">
+        <v>1</v>
       </c>
       <c r="AO470" t="inlineStr">
         <is>
@@ -73105,22 +74720,17 @@
       </c>
       <c r="AP470" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ470" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR470" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS470" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1195</t>
+          <t>SER_SG_CDA_ZIKA; SER_SG_HIST_ZIKA</t>
         </is>
       </c>
       <c r="AT470" t="n">
@@ -73128,47 +74738,47 @@
       </c>
       <c r="AU470" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV470" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW470" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX470" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY470" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ470" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA470" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB470" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC470" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73195,17 +74805,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -73239,39 +74849,17 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O471" t="n">
-        <v>0</v>
-      </c>
-      <c r="U471" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="V471" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
-      <c r="W471" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X471" t="inlineStr">
-        <is>
-          <t>Zika virus</t>
-        </is>
-      </c>
-      <c r="Y471" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z471" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0.0004668273620270607</v>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA471" t="inlineStr">
@@ -73279,135 +74867,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB471" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC471" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD471" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE471" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF471" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG471" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH471" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI471" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ471" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK471" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
-        </is>
-      </c>
-      <c r="AM471" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN471" t="b">
-        <v>1</v>
-      </c>
       <c r="AO471" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP471" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ471" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR471" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS471" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1195</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS471" t="inlineStr"/>
       <c r="AT471" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU471" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV471" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW471" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX471" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY471" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ471" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA471" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB471" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC471" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -73439,120 +74960,931 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
+      <c r="R472" t="n">
+        <v>0</v>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO472" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP472" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ472" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR472" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS472" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT472" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU472" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV472" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW472" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX472" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY472" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA472" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB472" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC472" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>0</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="W473" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>Zika virus</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB473" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC473" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD473" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE473" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF473" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG473" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI473" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ473" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK473" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1195.</t>
+        </is>
+      </c>
+      <c r="AM473" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN473" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO473" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP473" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ473" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR473" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS473" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1195</t>
+        </is>
+      </c>
+      <c r="AT473" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU473" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV473" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW473" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX473" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY473" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA473" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB473" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC473" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr">
+      <c r="G474" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>D051</t>
-        </is>
-      </c>
-      <c r="I472" t="inlineStr">
-        <is>
-          <t>Zika virus disease</t>
-        </is>
-      </c>
-      <c r="J472" t="inlineStr">
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
         <is>
           <t>寨卡病毒病</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr">
+      <c r="K474" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
+      <c r="L474" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M472" t="inlineStr">
+      <c r="M474" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N472" t="n">
-        <v>0</v>
-      </c>
-      <c r="O472" t="n">
-        <v>0</v>
-      </c>
-      <c r="R472" t="n">
-        <v>0</v>
-      </c>
-      <c r="S472" t="inlineStr">
+      <c r="N474" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0</v>
+      </c>
+      <c r="S474" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO472" t="inlineStr">
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO474" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP472" t="inlineStr">
+      <c r="AP474" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR472" t="inlineStr">
+      <c r="AR474" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS472" t="inlineStr"/>
-      <c r="AT472" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU472" t="inlineStr">
+      <c r="AS474" t="inlineStr"/>
+      <c r="AT474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU474" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV472" t="inlineStr">
+      <c r="AV474" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW472" t="inlineStr">
+      <c r="AW474" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX472" t="inlineStr">
+      <c r="AX474" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY472" t="inlineStr">
+      <c r="AY474" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ472" t="inlineStr">
+      <c r="AZ474" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA472" t="inlineStr">
+      <c r="BA474" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB472" t="inlineStr">
+      <c r="BB474" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC472" t="inlineStr">
+      <c r="BC474" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="R475" t="n">
+        <v>0</v>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA475" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO475" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP475" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ475" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR475" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS475" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT475" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU475" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV475" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW475" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX475" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY475" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA475" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB475" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC475" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W476" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>Zikafeber-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA476" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB476" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC476" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD476" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE476" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF476" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG476" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH476" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI476" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ476" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK476" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM476" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN476" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO476" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP476" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ476" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR476" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS476" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_513_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT476" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU476" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV476" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW476" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX476" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY476" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA476" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB476" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC476" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -73672,7 +76004,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10">
@@ -73682,7 +76014,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11">
@@ -73702,7 +76034,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d051/2026-2029.xlsx
+++ b/diseases/d051/2026-2029.xlsx
@@ -75888,6 +75888,151 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>zika-virus-disease</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
+      <c r="R477" t="n">
+        <v>0</v>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO477" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP477" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR477" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS477" t="inlineStr"/>
+      <c r="AT477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU477" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV477" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW477" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX477" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY477" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA477" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB477" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC477" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -75921,7 +76066,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -76004,7 +76149,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10">
@@ -76014,7 +76159,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11">
